--- a/tame_output/ON/bt/strategyON_20231129.xlsx
+++ b/tame_output/ON/bt/strategyON_20231129.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>92.5%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.3%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-156.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.1%</t>
+          <t>131.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.0%</t>
+          <t>125.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1795"/>
+  <dimension ref="A1:G1796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.139561641237695</v>
+        <v>3.136752015083875</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42811,6 +42811,29 @@
       </c>
       <c r="G1795" t="n">
         <v>4.393974528870945</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" s="2" t="n">
+        <v>45258</v>
+      </c>
+      <c r="B1796" t="n">
+        <v>3.160927146430493</v>
+      </c>
+      <c r="C1796" t="n">
+        <v>3.079594415968698</v>
+      </c>
+      <c r="D1796" t="n">
+        <v>1.561449084345071</v>
+      </c>
+      <c r="E1796" t="n">
+        <v>3.70381762539298</v>
+      </c>
+      <c r="F1796" t="n">
+        <v>2.185590138912724</v>
+      </c>
+      <c r="G1796" t="n">
+        <v>4.390948499316334</v>
       </c>
     </row>
   </sheetData>
